--- a/algoritmos/archivos/datos.xlsx
+++ b/algoritmos/archivos/datos.xlsx
@@ -1,112 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerson\Desktop\Python\Clases\Proye\algoritmos\archivos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5323B2C6-68C0-41B4-B181-603E1C4B3A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="clientes" sheetId="1" r:id="rId1"/>
-    <sheet name="inventario" sheetId="2" r:id="rId2"/>
-    <sheet name="ventas" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clientes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ventas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>codigo</t>
-  </si>
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>direccion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerson </t>
-  </si>
-  <si>
-    <t>Jalapa</t>
-  </si>
-  <si>
-    <t>Codigo</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Existencia</t>
-  </si>
-  <si>
-    <t>Proveedor</t>
-  </si>
-  <si>
-    <t>Precio</t>
-  </si>
-  <si>
-    <t>Lapiz</t>
-  </si>
-  <si>
-    <t>Bic</t>
-  </si>
-  <si>
-    <t>gorra</t>
-  </si>
-  <si>
-    <t>puma</t>
-  </si>
-  <si>
-    <t>codigo producto</t>
-  </si>
-  <si>
-    <t>codigo cliente</t>
-  </si>
-  <si>
-    <t>cantidad de productos</t>
-  </si>
-  <si>
-    <t>total de ventas</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,22 +56,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -406,30 +396,44 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>codigo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>direccion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jutiapa</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -438,63 +442,105 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623CD5D0-BCFA-4B19-98F6-B82FE9259C78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Codigo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Existencia</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lapiz</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bic</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gorra</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>puma</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crema</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>40</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D4" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -502,40 +548,53 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13A4956-DBD6-47AA-9B58-02B17FBA39B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col width="15.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13.42578125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="14.140625" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>codigo producto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>codigo cliente</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cantidad de productos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total de ventas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>201</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>2</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>400</v>
       </c>
     </row>

--- a/algoritmos/archivos/datos.xlsx
+++ b/algoritmos/archivos/datos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3435" yWindow="1515" windowWidth="15300" windowHeight="7785" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clientes" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,27 +11,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ventas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -55,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,15 +413,51 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>201</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Gerson</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jalapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Enrique</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jalapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Luis</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Jutiapa</t>
         </is>
@@ -478,56 +505,60 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lapiz</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bic</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Lapiz</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bic</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>8</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gorra</t>
+          <t>Mouse</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>puma</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crema</t>
+          <t>Bocina</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -535,11 +566,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -553,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -585,17 +616,39 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>201</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/algoritmos/archivos/datos.xlsx
+++ b/algoritmos/archivos/datos.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -651,6 +651,24 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/algoritmos/archivos/datos.xlsx
+++ b/algoritmos/archivos/datos.xlsx
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,23 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Jutiapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Erick</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Jalapa</t>
         </is>
       </c>
     </row>
@@ -474,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,6 +588,29 @@
       </c>
       <c r="E4" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3000</v>
       </c>
     </row>
   </sheetData>

--- a/algoritmos/archivos/datos.xlsx
+++ b/algoritmos/archivos/datos.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,6 +611,32 @@
       </c>
       <c r="E5" t="n">
         <v>3000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Dell</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
